--- a/data/trending_integrated_20261023_09.xlsx
+++ b/data/trending_integrated_20261023_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1196000</v>
+        <v>4295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'+14.53%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>800</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>560</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>1561</v>
+        <v>201</v>
       </c>
       <c r="H2" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1223000</v>
+        <v>3750</v>
       </c>
       <c r="K2" t="n">
-        <v>1200000</v>
+        <v>3905</v>
       </c>
       <c r="L2" t="n">
-        <v>1216000</v>
+        <v>4295</v>
       </c>
       <c r="M2" t="n">
-        <v>1195000</v>
+        <v>3815</v>
       </c>
       <c r="N2" t="n">
-        <v>48.79</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>275790078000</v>
+        <v>29553819621</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>7050</v>
       </c>
       <c r="Q2" t="n">
-        <v>468000</v>
+        <v>2500</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,29 +626,397 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>솔리다임 상장 중단 관련 내용. 일부 투자자는 이를 호재로 해석하나, 정치적 언급과 함께 부정적인 감정 표현도 나타남.</t>
+          <t>북한 관련 지정학적 이슈 및 미국 방산주 급등 관련 언급. 미국장 급락에도 불구하고 일부 긍정적 신호.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>['북한', '방산주', '미국장']</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>065450</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>59400</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'+7.22%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F3" t="n">
+        <v>59</v>
+      </c>
+      <c r="G3" t="n">
+        <v>355</v>
+      </c>
+      <c r="H3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>55400</v>
+      </c>
+      <c r="K3" t="n">
+        <v>56300</v>
+      </c>
+      <c r="L3" t="n">
+        <v>59600</v>
+      </c>
+      <c r="M3" t="n">
+        <v>56200</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="O3" t="n">
+        <v>173812561000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>외인·기관 대규모 순매수 및 자사주 매입/소각 관련 언급. 미국장 급락 및 금요일장이라는 변수 존재.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['외인', '기관', '자사주']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1188000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'-2.86%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>558</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H4" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1223000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1216000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1171000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="O4" t="n">
+        <v>577075534500</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>468000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>솔리다임 상장 철회(중단) 관련 언급. 국내외 반도체 업황 및 정치적 이슈 관련 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>0.1</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>['솔리다임', '상장 중단', '악재 해소']</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['솔리다임', '철회', '반도체']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
         <v>16</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>207000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-3.50%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>561</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1936</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>214500</v>
+      </c>
+      <c r="K5" t="n">
+        <v>206000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>209500</v>
+      </c>
+      <c r="M5" t="n">
+        <v>203500</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="O5" t="n">
+        <v>478673339500</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>정치적 언급 및 대통령 비판 위주의 내용. 반도체 산업 전반 및 공매도 관련 부정적 정서.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>58400</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-5.19%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E6" t="n">
+        <v>92</v>
+      </c>
+      <c r="F6" t="n">
+        <v>70</v>
+      </c>
+      <c r="G6" t="n">
+        <v>229</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>61600</v>
+      </c>
+      <c r="K6" t="n">
+        <v>59600</v>
+      </c>
+      <c r="L6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>57700</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15724921350</v>
+      </c>
+      <c r="P6" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>미국 증시 폭락 및 국내 증시 전반의 부정적 전망. 공매도 관련 이슈 언급.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['미국증시', '폭락', '공매도']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>034020</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261023_09.xlsx
+++ b/data/trending_integrated_20261023_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4295</v>
+        <v>4200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.53%</t>
+          <t>'+12.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>29553819621</v>
+        <v>42283099816</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 이슈 및 미국 방산주 급등 관련 언급. 미국장 급락에도 불구하고 일부 긍정적 신호.</t>
+          <t>북한 관련 지정학적 리스크 부각, 록히드마틴 급등 등 연관주 움직임과 함께 상승 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['북한', '방산주', '미국장']</t>
+          <t>['지정학적 리스크', '북한 도발', '록히드마틴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59400</v>
+        <v>58800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.22%</t>
+          <t>'+6.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>355</v>
+        <v>423</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -693,7 +693,7 @@
         <v>56300</v>
       </c>
       <c r="L3" t="n">
-        <v>59600</v>
+        <v>59700</v>
       </c>
       <c r="M3" t="n">
         <v>56200</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>173812561000</v>
+        <v>224429417500</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -711,23 +711,23 @@
         <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>321000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 대규모 순매수 및 자사주 매입/소각 관련 언급. 미국장 급락 및 금요일장이라는 변수 존재.</t>
+          <t>외인·기관 대규모 자사주 매입 및 소각 효과 기대, MSCI 패시브 자금 유입 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['외인', '기관', '자사주']</t>
+          <t>['자사주 매입', 'MSCI', '패시브 자금']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1188000</v>
+        <v>8910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>558</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>1450</v>
+        <v>103</v>
       </c>
       <c r="H4" t="n">
-        <v>48.77</v>
+        <v>5.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1223000</v>
+        <v>8680</v>
       </c>
       <c r="K4" t="n">
-        <v>1200000</v>
+        <v>9410</v>
       </c>
       <c r="L4" t="n">
-        <v>1216000</v>
+        <v>9460</v>
       </c>
       <c r="M4" t="n">
-        <v>1171000</v>
+        <v>8810</v>
       </c>
       <c r="N4" t="n">
-        <v>48.79</v>
+        <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>577075534500</v>
+        <v>3702420875</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>468000</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-176000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회(중단) 관련 언급. 국내외 반도체 업황 및 정치적 이슈 관련 부정적 전망.</t>
+          <t>뇌졸중 치료제 관련 특허 언급 있으나, 약효 증명 및 상장 관련 불확실성으로 인한 부정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['솔리다임', '철회', '반도체']</t>
+          <t>['뇌졸중 치료제', '특허', '약효 증명']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>207000</v>
+        <v>1187000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-3.50%</t>
+          <t>'-2.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G5" t="n">
-        <v>1936</v>
+        <v>1342</v>
       </c>
       <c r="H5" t="n">
-        <v>46.13</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>214500</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>206000</v>
+        <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>209500</v>
+        <v>1216000</v>
       </c>
       <c r="M5" t="n">
-        <v>203500</v>
+        <v>1171000</v>
       </c>
       <c r="N5" t="n">
-        <v>46.14</v>
+        <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>478673339500</v>
+        <v>734818861500</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-154000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 언급 및 대통령 비판 위주의 내용. 반도체 산업 전반 및 공매도 관련 부정적 정서.</t>
+          <t>솔리다임 미국 상장 중단 관련 복합적인 반응, 정치적 이슈와 연관된 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['솔리다임', '상장 중단', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58400</v>
+        <v>205750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-5.19%</t>
+          <t>'-4.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>573</v>
       </c>
       <c r="G6" t="n">
-        <v>229</v>
+        <v>1829</v>
       </c>
       <c r="H6" t="n">
-        <v>22.25</v>
+        <v>46.13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,58 +963,150 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>61600</v>
+        <v>214500</v>
       </c>
       <c r="K6" t="n">
-        <v>59600</v>
+        <v>206000</v>
       </c>
       <c r="L6" t="n">
-        <v>60000</v>
+        <v>209500</v>
       </c>
       <c r="M6" t="n">
-        <v>57700</v>
+        <v>203500</v>
       </c>
       <c r="N6" t="n">
-        <v>22.26</v>
+        <v>46.14</v>
       </c>
       <c r="O6" t="n">
-        <v>15724921350</v>
+        <v>606747902250</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-261000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 국내 증시 전반의 부정적 전망. 공매도 관련 이슈 언급.</t>
+          <t>정치적 이슈와 공매도 관련 부정적 언급, 실질적인 주가 상승 근거 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['미국증시', '폭락', '공매도']</t>
+          <t>['공매도', '정치적 이슈', '적정가']</t>
         </is>
       </c>
       <c r="X6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>58100</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-5.68%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>106</v>
+      </c>
+      <c r="F7" t="n">
+        <v>77</v>
+      </c>
+      <c r="G7" t="n">
+        <v>295</v>
+      </c>
+      <c r="H7" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>61600</v>
+      </c>
+      <c r="K7" t="n">
+        <v>59600</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>57700</v>
+      </c>
+      <c r="N7" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20783779650</v>
+      </c>
+      <c r="P7" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>35000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>미 증시 폭락 및 공매도 관련 우려, 주가 하락에 대한 부정적인 전망 다수.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['공매도', '미 증시', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>2</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>034020</t>
         </is>

--- a/data/trending_integrated_20261023_09.xlsx
+++ b/data/trending_integrated_20261023_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4200</v>
+        <v>4380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.00%</t>
+          <t>'+16.80%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>3905</v>
       </c>
       <c r="L2" t="n">
-        <v>4295</v>
+        <v>4395</v>
       </c>
       <c r="M2" t="n">
         <v>3815</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>42283099816</v>
+        <v>53277362320</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -619,14 +619,14 @@
         <v>2500</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-209000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각, 록히드마틴 급등 등 연관주 움직임과 함께 상승 기대감.</t>
+          <t>북한 도발 관련 지정학적 리스크 부각 및 방산주 록히드마틴 급등 영향. 외인 매물 부담 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '북한 도발', '록히드마틴']</t>
+          <t>['북한 도발', '방산주', '록히드마틴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>224429417500</v>
+        <v>258279966600</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 대규모 자사주 매입 및 소각 효과 기대, MSCI 패시브 자금 유입 전망.</t>
+          <t>외인·기관 대규모 자사주 매입 발표에 따른 주가 방어 및 상승 기대감. MSCI 패시브 자금 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI', '패시브 자금']</t>
+          <t>['자사주 매입', 'MSCI', '외인 수급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8910</v>
+        <v>8810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.65%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
         <v>5.11</v>
@@ -788,13 +788,13 @@
         <v>9460</v>
       </c>
       <c r="M4" t="n">
-        <v>8810</v>
+        <v>8700</v>
       </c>
       <c r="N4" t="n">
         <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3702420875</v>
+        <v>4134156365</v>
       </c>
       <c r="P4" t="n">
         <v>15900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 언급 있으나, 약효 증명 및 상장 관련 불확실성으로 인한 부정적 전망.</t>
+          <t>신약 개발 및 임상 성공 관련 기대감 언급되나, 과거 허풍제약 비판 및 약효 증명 미흡 지적.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['뇌졸중 치료제', '특허', '약효 증명']</t>
+          <t>['신약 개발', '임상 성공', '특허']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1187000</v>
+        <v>7120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>562</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>1342</v>
+        <v>142</v>
       </c>
       <c r="H5" t="n">
-        <v>48.77</v>
+        <v>25.42</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1223000</v>
+        <v>7230</v>
       </c>
       <c r="K5" t="n">
-        <v>1200000</v>
+        <v>7100</v>
       </c>
       <c r="L5" t="n">
-        <v>1216000</v>
+        <v>7170</v>
       </c>
       <c r="M5" t="n">
-        <v>1171000</v>
+        <v>7010</v>
       </c>
       <c r="N5" t="n">
-        <v>48.79</v>
+        <v>25.47</v>
       </c>
       <c r="O5" t="n">
-        <v>734818861500</v>
+        <v>3782521620</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q5" t="n">
-        <v>468000</v>
+        <v>7010</v>
       </c>
       <c r="R5" t="n">
-        <v>-154000</v>
+        <v>17000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 미국 상장 중단 관련 복합적인 반응, 정치적 이슈와 연관된 부정적 언급 다수.</t>
+          <t>분기 순이익 7,556억 달성으로 재무 상태 개선. 목표가 하향 보고서 언급되며 투자 판단 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장 중단', '정치적 이슈']</t>
+          <t>['순이익', '컨센서스', '재무 개선']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205750</v>
+        <v>1202000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-4.08%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="G6" t="n">
-        <v>1829</v>
+        <v>1346</v>
       </c>
       <c r="H6" t="n">
-        <v>46.13</v>
+        <v>48.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>214500</v>
+        <v>1223000</v>
       </c>
       <c r="K6" t="n">
-        <v>206000</v>
+        <v>1200000</v>
       </c>
       <c r="L6" t="n">
-        <v>209500</v>
+        <v>1216000</v>
       </c>
       <c r="M6" t="n">
-        <v>203500</v>
+        <v>1171000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.14</v>
+        <v>48.79</v>
       </c>
       <c r="O6" t="n">
-        <v>606747902250</v>
+        <v>887436717500</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R6" t="n">
-        <v>-261000</v>
+        <v>-154000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 공매도 관련 부정적 언급, 실질적인 주가 상승 근거 부족.</t>
+          <t>솔리다임 상장 철회 관련 악재 해소 기대감과 함께 정치적 이슈에 대한 부정적 언급. 투자 불확실성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '정치적 이슈', '적정가']</t>
+          <t>['솔리다임', '상장 철회', '정치 이슈']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58100</v>
+        <v>207500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-5.68%</t>
+          <t>'-3.26%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>570</v>
       </c>
       <c r="G7" t="n">
-        <v>295</v>
+        <v>1757</v>
       </c>
       <c r="H7" t="n">
-        <v>22.25</v>
+        <v>46.13</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>61600</v>
+        <v>214500</v>
       </c>
       <c r="K7" t="n">
-        <v>59600</v>
+        <v>206000</v>
       </c>
       <c r="L7" t="n">
-        <v>60000</v>
+        <v>209500</v>
       </c>
       <c r="M7" t="n">
-        <v>57700</v>
+        <v>203500</v>
       </c>
       <c r="N7" t="n">
-        <v>22.26</v>
+        <v>46.14</v>
       </c>
       <c r="O7" t="n">
-        <v>20783779650</v>
+        <v>724621810500</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>35000</v>
+        <v>-261000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미 증시 폭락 및 공매도 관련 우려, 주가 하락에 대한 부정적인 전망 다수.</t>
+          <t>정치적 이슈에 대한 강한 불만 제기. 주가 관련 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,20 +1095,204 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '미 증시', '주가 하락']</t>
+          <t>['공매도 금지', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>58700</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-4.71%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E8" t="n">
+        <v>118</v>
+      </c>
+      <c r="F8" t="n">
+        <v>85</v>
+      </c>
+      <c r="G8" t="n">
+        <v>322</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>61600</v>
+      </c>
+      <c r="K8" t="n">
+        <v>59600</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>57700</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>25855635550</v>
+      </c>
+      <c r="P8" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미국 증시 폭락 영향 및 공매도 물량 증가로 인한 하락세 우려. 정부 대응 부재 비판.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['공매도', '미국 증시', '하락 추세']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>2</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9410</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-6.74%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>47</v>
+      </c>
+      <c r="F9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G9" t="n">
+        <v>143</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10090</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9770</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10060</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9310</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14803366875</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R9" t="n">
+        <v>40000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>단기 급등 후 조정 및 횡보 예상. 투자 주의 해지 관련 언급 외 객관적 근거 부족.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['조정', '횡보', '투자 주의']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>396300</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261023_09.xlsx
+++ b/data/trending_integrated_20261023_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4380</v>
+        <v>4490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.80%</t>
+          <t>'+19.73%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>3905</v>
       </c>
       <c r="L2" t="n">
-        <v>4395</v>
+        <v>4515</v>
       </c>
       <c r="M2" t="n">
         <v>3815</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>53277362320</v>
+        <v>71565486752</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 도발 관련 지정학적 리스크 부각 및 방산주 록히드마틴 급등 영향. 외인 매물 부담 언급.</t>
+          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 기대감이 있으나, 미증시 폭락으로 인한 변동성 우려.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['북한 도발', '방산주', '록히드마틴']</t>
+          <t>['북한 리스크', '방산주', '변동성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58800</v>
+        <v>58900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.14%</t>
+          <t>'+6.32%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>258279966600</v>
+        <v>272622910200</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 대규모 자사주 매입 발표에 따른 주가 방어 및 상승 기대감. MSCI 패시브 자금 유입 가능성 언급.</t>
+          <t>외인·기관의 대규모 매수세 유입과 자사주 매입/소각 기대감으로 인한 주가 상승 전망. MSCI 편입 확정적이라는 분석.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI', '외인 수급']</t>
+          <t>['외인', '기관', 'MSCI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8810</v>
+        <v>18000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+3.75%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>0.48</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>5.11</v>
+        <v>3.77</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8680</v>
+        <v>17350</v>
       </c>
       <c r="K4" t="n">
-        <v>9410</v>
+        <v>18130</v>
       </c>
       <c r="L4" t="n">
-        <v>9460</v>
+        <v>19070</v>
       </c>
       <c r="M4" t="n">
-        <v>8700</v>
+        <v>17750</v>
       </c>
       <c r="N4" t="n">
-        <v>5.15</v>
+        <v>3.29</v>
       </c>
       <c r="O4" t="n">
-        <v>4134156365</v>
+        <v>33698248285</v>
       </c>
       <c r="P4" t="n">
-        <v>15900</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>6310</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-176000</v>
+        <v>-50000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신약 개발 및 임상 성공 관련 기대감 언급되나, 과거 허풍제약 비판 및 약효 증명 미흡 지적.</t>
+          <t>미국 보안주 상승에 따른 동반 상승 기대감과 AI 해킹 관련 뉴스로 인한 잠재적 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신약 개발', '임상 성공', '특허']</t>
+          <t>['보안주', 'AI 해킹', '성장 기대']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7120</v>
+        <v>8820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="H5" t="n">
-        <v>25.42</v>
+        <v>5.11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7230</v>
+        <v>8680</v>
       </c>
       <c r="K5" t="n">
-        <v>7100</v>
+        <v>9410</v>
       </c>
       <c r="L5" t="n">
-        <v>7170</v>
+        <v>9460</v>
       </c>
       <c r="M5" t="n">
-        <v>7010</v>
+        <v>8700</v>
       </c>
       <c r="N5" t="n">
-        <v>25.47</v>
+        <v>5.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3782521620</v>
+        <v>4408173015</v>
       </c>
       <c r="P5" t="n">
-        <v>17950</v>
+        <v>15900</v>
       </c>
       <c r="Q5" t="n">
-        <v>7010</v>
+        <v>6310</v>
       </c>
       <c r="R5" t="n">
-        <v>17000</v>
+        <v>-176000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>분기 순이익 7,556억 달성으로 재무 상태 개선. 목표가 하향 보고서 언급되며 투자 판단 혼재.</t>
+          <t>신약 개발 관련 기대감과 특허 소식이 있으나, 약효 증명 실패 및 부정적인 여론으로 인해 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['순이익', '컨센서스', '재무 개선']</t>
+          <t>['신약 개발', '특허', '주가 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1202000</v>
+        <v>7120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>560</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>1346</v>
+        <v>181</v>
       </c>
       <c r="H6" t="n">
-        <v>48.77</v>
+        <v>25.42</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1223000</v>
+        <v>7230</v>
       </c>
       <c r="K6" t="n">
-        <v>1200000</v>
+        <v>7100</v>
       </c>
       <c r="L6" t="n">
-        <v>1216000</v>
+        <v>7170</v>
       </c>
       <c r="M6" t="n">
-        <v>1171000</v>
+        <v>7010</v>
       </c>
       <c r="N6" t="n">
-        <v>48.79</v>
+        <v>25.47</v>
       </c>
       <c r="O6" t="n">
-        <v>887436717500</v>
+        <v>4149666785</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>7010</v>
       </c>
       <c r="R6" t="n">
-        <v>-154000</v>
+        <v>17000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 관련 악재 해소 기대감과 함께 정치적 이슈에 대한 부정적 언급. 투자 불확실성.</t>
+          <t>기록적인 분기 순이익 달성 소식에도 불구하고 목표가 하향 및 파산 우려 등 상반된 의견이 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장 철회', '정치 이슈']</t>
+          <t>['순이익', '목표가 하향', '파산 우려']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207500</v>
+        <v>1193000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.26%</t>
+          <t>'-2.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="G7" t="n">
-        <v>1757</v>
+        <v>1239</v>
       </c>
       <c r="H7" t="n">
-        <v>46.13</v>
+        <v>48.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>214500</v>
+        <v>1223000</v>
       </c>
       <c r="K7" t="n">
-        <v>206000</v>
+        <v>1200000</v>
       </c>
       <c r="L7" t="n">
-        <v>209500</v>
+        <v>1216000</v>
       </c>
       <c r="M7" t="n">
-        <v>203500</v>
+        <v>1171000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.14</v>
+        <v>48.79</v>
       </c>
       <c r="O7" t="n">
-        <v>724621810500</v>
+        <v>1010876438500</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>468000</v>
       </c>
       <c r="R7" t="n">
-        <v>-261000</v>
+        <v>-154000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 강한 불만 제기. 주가 관련 객관적 근거 부족.</t>
+          <t>솔리다임 상장 철회 이슈와 정치적 불만, 공매도 관련 부정적 언급이 혼재하며 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도 금지', '정치적 이슈']</t>
+          <t>['솔리다임', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58700</v>
+        <v>206000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-4.71%</t>
+          <t>'-3.96%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>564</v>
       </c>
       <c r="G8" t="n">
-        <v>322</v>
+        <v>1755</v>
       </c>
       <c r="H8" t="n">
-        <v>22.25</v>
+        <v>46.13</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>61600</v>
+        <v>214500</v>
       </c>
       <c r="K8" t="n">
-        <v>59600</v>
+        <v>206000</v>
       </c>
       <c r="L8" t="n">
-        <v>60000</v>
+        <v>209500</v>
       </c>
       <c r="M8" t="n">
-        <v>57700</v>
+        <v>203500</v>
       </c>
       <c r="N8" t="n">
-        <v>22.26</v>
+        <v>46.14</v>
       </c>
       <c r="O8" t="n">
-        <v>25855635550</v>
+        <v>824287683000</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>35000</v>
+        <v>-261000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 영향 및 공매도 물량 증가로 인한 하락세 우려. 정부 대응 부재 비판.</t>
+          <t>정치적 이슈와 관련된 부정적인 게시글이 주를 이루며, 주가 하락에 대한 불만이 표출되고 있음.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '미국 증시', '하락 추세']</t>
+          <t>['정치', '주가 하락', '불만']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9410</v>
+        <v>16580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-6.74%</t>
+          <t>'-4.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.19</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>27.89</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10090</v>
+        <v>17320</v>
       </c>
       <c r="K9" t="n">
-        <v>9770</v>
+        <v>16810</v>
       </c>
       <c r="L9" t="n">
-        <v>10060</v>
+        <v>16850</v>
       </c>
       <c r="M9" t="n">
-        <v>9310</v>
+        <v>16450</v>
       </c>
       <c r="N9" t="n">
-        <v>3.69</v>
+        <v>27.87</v>
       </c>
       <c r="O9" t="n">
-        <v>14803366875</v>
+        <v>8638705865</v>
       </c>
       <c r="P9" t="n">
-        <v>11690</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>2270</v>
+        <v>16450</v>
       </c>
       <c r="R9" t="n">
-        <v>40000</v>
+        <v>-36000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 급등 후 조정 및 횡보 예상. 투자 주의 해지 관련 언급 외 객관적 근거 부족.</t>
+          <t>주주 환원 정책 발표 가능성에도 불구하고 주가 하락세가 지속되며, 투자자들의 불만과 불안감이 고조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,18 +1279,202 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['조정', '횡보', '투자 주의']</t>
+          <t>['주가 하락', '주주 환원', '불만']</t>
         </is>
       </c>
       <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>58500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-5.03%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E10" t="n">
+        <v>131</v>
+      </c>
+      <c r="F10" t="n">
+        <v>94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>327</v>
+      </c>
+      <c r="H10" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>61600</v>
+      </c>
+      <c r="K10" t="n">
+        <v>59600</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>57700</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>33259684950</v>
+      </c>
+      <c r="P10" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>미국 증시 폭락 영향 및 공매도 물량 증가로 인한 하락세 우려. 정부 대응 부재 비판.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['공매도', '미국 증시', '하락 추세']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9490</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-5.95%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>38</v>
+      </c>
+      <c r="G11" t="n">
+        <v>161</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>10090</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9770</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10060</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9280</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17560716255</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>로봇 관련 테마에서 소외되고 차트상 하락 추세가 예상되며, 투자자들의 부정적인 전망과 우려가 지배적.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['로봇 테마', '하락 추세', '부정적 전망']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>6</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261023_09.xlsx
+++ b/data/trending_integrated_20261023_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4490</v>
+        <v>4255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.73%</t>
+          <t>'+13.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>3905</v>
       </c>
       <c r="L2" t="n">
-        <v>4515</v>
+        <v>4550</v>
       </c>
       <c r="M2" t="n">
         <v>3815</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>71565486752</v>
+        <v>87307971413</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 기대감이 있으나, 미증시 폭락으로 인한 변동성 우려.</t>
+          <t>북한 도발 관련 방산주 상승 기대감 및 미 증시 폭락 속 록히드마틴 급등 영향. 외인 매도 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['북한 리스크', '방산주', '변동성']</t>
+          <t>['북한 도발', '방산주', '록히드마틴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58900</v>
+        <v>60000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.32%</t>
+          <t>'+8.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>494</v>
+        <v>551</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -693,7 +693,7 @@
         <v>56300</v>
       </c>
       <c r="L3" t="n">
-        <v>59700</v>
+        <v>60400</v>
       </c>
       <c r="M3" t="n">
         <v>56200</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>272622910200</v>
+        <v>352349432050</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -711,14 +711,14 @@
         <v>23150</v>
       </c>
       <c r="R3" t="n">
-        <v>321000</v>
+        <v>824000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관의 대규모 매수세 유입과 자사주 매입/소각 기대감으로 인한 주가 상승 전망. MSCI 편입 확정적이라는 분석.</t>
+          <t>외인·기관 대규모 순매수와 자사주 매입 예정에 따른 주가 방어 및 상승 기대감. MSCI 편입 및 목표가 상향 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['외인', '기관', 'MSCI']</t>
+          <t>['자사주 매입', 'MSCI 편입', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18000</v>
+        <v>8780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.75%</t>
+          <t>'+1.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.48</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="H4" t="n">
-        <v>3.77</v>
+        <v>5.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17350</v>
+        <v>8680</v>
       </c>
       <c r="K4" t="n">
-        <v>18130</v>
+        <v>9410</v>
       </c>
       <c r="L4" t="n">
-        <v>19070</v>
+        <v>9460</v>
       </c>
       <c r="M4" t="n">
-        <v>17750</v>
+        <v>8700</v>
       </c>
       <c r="N4" t="n">
-        <v>3.29</v>
+        <v>5.15</v>
       </c>
       <c r="O4" t="n">
-        <v>33698248285</v>
+        <v>4680786385</v>
       </c>
       <c r="P4" t="n">
-        <v>22450</v>
+        <v>15900</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>6310</v>
       </c>
       <c r="R4" t="n">
-        <v>-50000</v>
+        <v>-186000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 보안주 상승에 따른 동반 상승 기대감과 AI 해킹 관련 뉴스로 인한 잠재적 성장 가능성 언급.</t>
+          <t>전 세계 특허 획득 및 3상 성공 가능성에도 불구하고 약효 증명 부족으로 인한 주가 하락. 주포 장난질 및 허풍제약 비판.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', 'AI 해킹', '성장 기대']</t>
+          <t>['특허 획득', '3상 성공', '약효 증명']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8820</v>
+        <v>17220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
-        <v>5.11</v>
+        <v>3.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8680</v>
+        <v>17350</v>
       </c>
       <c r="K5" t="n">
-        <v>9410</v>
+        <v>18130</v>
       </c>
       <c r="L5" t="n">
-        <v>9460</v>
+        <v>19070</v>
       </c>
       <c r="M5" t="n">
-        <v>8700</v>
+        <v>17220</v>
       </c>
       <c r="N5" t="n">
-        <v>5.15</v>
+        <v>3.29</v>
       </c>
       <c r="O5" t="n">
-        <v>4408173015</v>
+        <v>36340809645</v>
       </c>
       <c r="P5" t="n">
-        <v>15900</v>
+        <v>22450</v>
       </c>
       <c r="Q5" t="n">
-        <v>6310</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>-176000</v>
+        <v>-50000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신약 개발 관련 기대감과 특허 소식이 있으나, 약효 증명 실패 및 부정적인 여론으로 인해 주가 하락 우려.</t>
+          <t>미국 보안주 급등 속 라온시큐어 주가 하락 및 수급 부진 우려. AI 해킹 이슈에 따른 보안주 관심 증가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약 개발', '특허', '주가 하락']</t>
+          <t>['미국 보안주', 'AI 해킹', '수급 부진']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7120</v>
+        <v>7160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-0.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="H6" t="n">
         <v>25.42</v>
@@ -969,7 +969,7 @@
         <v>7100</v>
       </c>
       <c r="L6" t="n">
-        <v>7170</v>
+        <v>7190</v>
       </c>
       <c r="M6" t="n">
         <v>7010</v>
@@ -978,7 +978,7 @@
         <v>25.47</v>
       </c>
       <c r="O6" t="n">
-        <v>4149666785</v>
+        <v>4830236955</v>
       </c>
       <c r="P6" t="n">
         <v>17950</v>
@@ -987,23 +987,23 @@
         <v>7010</v>
       </c>
       <c r="R6" t="n">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>기록적인 분기 순이익 달성 소식에도 불구하고 목표가 하향 및 파산 우려 등 상반된 의견이 혼재.</t>
+          <t>분기 순이익 7,556억 달성과 재무 상태 개선에도 불구하고 목표가 하향 및 적자 예상에 대한 상반된 의견. FLiPP 개발 성공에 따른 주가 재평가 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['순이익', '목표가 하향', '파산 우려']</t>
+          <t>['순이익', '재무 개선', 'FLiPP']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1193000</v>
+        <v>1209000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.45%</t>
+          <t>'-1.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="G7" t="n">
-        <v>1239</v>
+        <v>1262</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1061,7 +1061,7 @@
         <v>1200000</v>
       </c>
       <c r="L7" t="n">
-        <v>1216000</v>
+        <v>1220000</v>
       </c>
       <c r="M7" t="n">
         <v>1171000</v>
@@ -1070,7 +1070,7 @@
         <v>48.79</v>
       </c>
       <c r="O7" t="n">
-        <v>1010876438500</v>
+        <v>1155499686500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1079,14 +1079,14 @@
         <v>468000</v>
       </c>
       <c r="R7" t="n">
-        <v>-154000</v>
+        <v>-272000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 이슈와 정치적 불만, 공매도 관련 부정적 언급이 혼재하며 주가 하락에 대한 우려.</t>
+          <t>솔리다임 상장 철회와 관련된 부정적 이슈 및 기관의 억지 매수 방어에 대한 비판. 외국인 매수 재개 및 목표가 상향 의견도 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['솔리다임', '공매도', '주가 하락']</t>
+          <t>['솔리다임', '기관 매수', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>206000</v>
+        <v>9930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.96%</t>
+          <t>'-1.59%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>564</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>1755</v>
+        <v>164</v>
       </c>
       <c r="H8" t="n">
-        <v>46.13</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>214500</v>
+        <v>10090</v>
       </c>
       <c r="K8" t="n">
-        <v>206000</v>
+        <v>9770</v>
       </c>
       <c r="L8" t="n">
-        <v>209500</v>
+        <v>10060</v>
       </c>
       <c r="M8" t="n">
-        <v>203500</v>
+        <v>9280</v>
       </c>
       <c r="N8" t="n">
-        <v>46.14</v>
+        <v>3.69</v>
       </c>
       <c r="O8" t="n">
-        <v>824287683000</v>
+        <v>21982856955</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>11690</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>2270</v>
       </c>
       <c r="R8" t="n">
-        <v>-261000</v>
+        <v>40000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적인 게시글이 주를 이루며, 주가 하락에 대한 불만이 표출되고 있음.</t>
+          <t>로봇 관련 테마에서 소외되고 차트상 하락 추세가 예상되며, 투자자들의 부정적인 전망과 우려가 지배적.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['정치', '주가 하락', '불만']</t>
+          <t>['로봇 테마', '하락 추세', '부정적 전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16580</v>
+        <v>208500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-4.27%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>557</v>
       </c>
       <c r="G9" t="n">
-        <v>66</v>
+        <v>1615</v>
       </c>
       <c r="H9" t="n">
-        <v>27.89</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17320</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>16810</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>16850</v>
+        <v>209500</v>
       </c>
       <c r="M9" t="n">
-        <v>16450</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>27.87</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>8638705865</v>
+        <v>930924939000</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>16450</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-36000</v>
+        <v>-319000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>113000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주주 환원 정책 발표 가능성에도 불구하고 주가 하락세가 지속되며, 투자자들의 불만과 불안감이 고조.</t>
+          <t>현 정부 정책 및 정치적 이슈에 대한 부정적 의견과 함께 주가 하락 우려 제기. 최저점 매수 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가 하락', '주주 환원', '불만']</t>
+          <t>['정치적 이슈', '주가 하락', '최저점']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58500</v>
+        <v>16720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.03%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="H10" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K10" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L10" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M10" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N10" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O10" t="n">
-        <v>33259684950</v>
+        <v>10077443735</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R10" t="n">
-        <v>35000</v>
+        <v>-46000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 영향 및 공매도 물량 증가로 인한 하락세 우려. 정부 대응 부재 비판.</t>
+          <t>지속적인 신저점 기록 및 주주 환원 정책 발표 가능성에도 불구하고 하락 추세 지속. 개미 투자자 꼬임 방지 및 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '미국 증시', '하락 추세']</t>
+          <t>['신저점', '주주 환원', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9490</v>
+        <v>59100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.95%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.19</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>161</v>
+        <v>340</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5</v>
+        <v>22.25</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10090</v>
+        <v>61600</v>
       </c>
       <c r="K11" t="n">
-        <v>9770</v>
+        <v>59600</v>
       </c>
       <c r="L11" t="n">
-        <v>10060</v>
+        <v>60000</v>
       </c>
       <c r="M11" t="n">
-        <v>9280</v>
+        <v>57700</v>
       </c>
       <c r="N11" t="n">
-        <v>3.69</v>
+        <v>22.26</v>
       </c>
       <c r="O11" t="n">
-        <v>17560716255</v>
+        <v>39109661950</v>
       </c>
       <c r="P11" t="n">
-        <v>11690</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>2270</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>40000</v>
+        <v>-25000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-69000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>로봇 관련 테마에서 소외되고 차트상 하락 추세가 예상되며, 투자자들의 부정적인 전망과 우려가 지배적.</t>
+          <t>미 증시 폭락 영향 및 공매도 누적에 따른 주가 하락 우려. 정부 부재 및 국민연금 방어 실패에 대한 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇 테마', '하락 추세', '부정적 전망']</t>
+          <t>['미 증시 폭락', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
